--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
   <si>
     <t/>
   </si>
   <si>
-    <t>20003405</t>
-  </si>
-  <si>
-    <t>FORVITA MARGARINE200</t>
+    <t>20104077</t>
+  </si>
+  <si>
+    <t>SEDAP KCP SPCL 725G</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -28,97 +28,115 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10008819</t>
-  </si>
-  <si>
-    <t>BANGO KECAP MNS 700G</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20117107</t>
+  </si>
+  <si>
+    <t>BANGO KECAP MNS 735</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20135312</t>
+  </si>
+  <si>
+    <t>WOW SPAGHETI CARB80</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20112371</t>
-  </si>
-  <si>
-    <t>GADJAH KP.TUBRUK 138</t>
+    <t>20135313</t>
+  </si>
+  <si>
+    <t>WOW SPAGHETI BOLOG76</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10003569</t>
-  </si>
-  <si>
-    <t>CLOSE UP GRN E.FR160</t>
+    <t>10036685</t>
+  </si>
+  <si>
+    <t>NUTELLA JAM HZLNT200</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20060393</t>
-  </si>
-  <si>
-    <t>NUVO CAIR CLSC 400</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20047217</t>
+  </si>
+  <si>
+    <t>PEPSODENT WHITE 225G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20042866</t>
-  </si>
-  <si>
-    <t>GRNIER ACNO FIGHT150</t>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20060386</t>
+  </si>
+  <si>
+    <t>GIV BW MLB&amp;CLG PC400</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20067449</t>
-  </si>
-  <si>
-    <t>GLW&amp;LOVELY DRM.GL100</t>
+    <t>20138029</t>
+  </si>
+  <si>
+    <t>GIV BW SAKURA 400ML</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20071105</t>
-  </si>
-  <si>
-    <t>MITU GP PURPLE 2X50S</t>
+    <t>20092317</t>
+  </si>
+  <si>
+    <t>POISE FAC.FM WHT 100</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20027095</t>
-  </si>
-  <si>
-    <t>MY BABY TELON PLS 60</t>
+    <t>20100027</t>
+  </si>
+  <si>
+    <t>POSH HJB GRN BLOS150</t>
   </si>
   <si>
     <t>9</t>
+  </si>
+  <si>
+    <t>20100662</t>
+  </si>
+  <si>
+    <t>POSH HJB PUR WISH150</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10000425</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH 60</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
   </si>
 </sst>
 </file>
@@ -511,12 +529,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -574,118 +593,118 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -694,30 +713,90 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="F11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>24</v>
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
   <si>
     <t/>
   </si>
   <si>
-    <t>20104077</t>
-  </si>
-  <si>
-    <t>SEDAP KCP SPCL 725G</t>
+    <t>20087284</t>
+  </si>
+  <si>
+    <t>SASA SANTAN KLP 200</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -28,115 +28,94 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20113150</t>
+  </si>
+  <si>
+    <t>SIMBA CRL CC STRW 34</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20117107</t>
-  </si>
-  <si>
-    <t>BANGO KECAP MNS 735</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20135312</t>
-  </si>
-  <si>
-    <t>WOW SPAGHETI CARB80</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20135313</t>
-  </si>
-  <si>
-    <t>WOW SPAGHETI BOLOG76</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10036685</t>
-  </si>
-  <si>
-    <t>NUTELLA JAM HZLNT200</t>
+    <t>20014069</t>
+  </si>
+  <si>
+    <t>FF UHT FULL CRM 946</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
+    <t>20014071</t>
+  </si>
+  <si>
+    <t>FF UHT CHOCO 946ML</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20127600</t>
+  </si>
+  <si>
+    <t>CPTADEN JB C.MINT225</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20031215</t>
+  </si>
+  <si>
+    <t>BIORE BF LIVELY 400</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20009500</t>
+  </si>
+  <si>
+    <t>BIORE B.FOAM RELX400</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20082205</t>
+  </si>
+  <si>
+    <t>SERASOFT SHP HFT 170</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20090023</t>
+  </si>
+  <si>
+    <t>WRDH BRGH MUG CLY100</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20047217</t>
-  </si>
-  <si>
-    <t>PEPSODENT WHITE 225G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20060386</t>
-  </si>
-  <si>
-    <t>GIV BW MLB&amp;CLG PC400</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20138029</t>
-  </si>
-  <si>
-    <t>GIV BW SAKURA 400ML</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20092317</t>
-  </si>
-  <si>
-    <t>POISE FAC.FM WHT 100</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20100027</t>
-  </si>
-  <si>
-    <t>POSH HJB GRN BLOS150</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20100662</t>
-  </si>
-  <si>
-    <t>POSH HJB PUR WISH150</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>10000425</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH 60</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
   </si>
 </sst>
 </file>
@@ -529,14 +508,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -593,10 +572,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -616,35 +595,35 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -653,10 +632,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -676,24 +655,24 @@
         <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>5</v>
@@ -701,19 +680,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>5</v>
@@ -721,82 +700,42 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
   <si>
     <t/>
   </si>
   <si>
-    <t>20087284</t>
-  </si>
-  <si>
-    <t>SASA SANTAN KLP 200</t>
+    <t>20055496</t>
+  </si>
+  <si>
+    <t>PRO CHIZ SPRD 160G</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -28,94 +28,100 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20113150</t>
-  </si>
-  <si>
-    <t>SIMBA CRL CC STRW 34</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20117107</t>
+  </si>
+  <si>
+    <t>BANGO KECAP MNS 735</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20114755</t>
+  </si>
+  <si>
+    <t>SDP MIE SPC.LAKSA 83</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20014069</t>
-  </si>
-  <si>
-    <t>FF UHT FULL CRM 946</t>
+    <t>10023792</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE SOTO 76GR</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20014071</t>
-  </si>
-  <si>
-    <t>FF UHT CHOCO 946ML</t>
+    <t>20047217</t>
+  </si>
+  <si>
+    <t>PEPSODENT WHITE 225G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20127600</t>
-  </si>
-  <si>
-    <t>CPTADEN JB C.MINT225</t>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20138272</t>
+  </si>
+  <si>
+    <t>LRST BB.WIPE SB 2X50</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20031215</t>
-  </si>
-  <si>
-    <t>BIORE BF LIVELY 400</t>
+    <t>20041399</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW LMN 400</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>20009500</t>
-  </si>
-  <si>
-    <t>BIORE B.FOAM RELX400</t>
+    <t>20120379</t>
+  </si>
+  <si>
+    <t>EMERON HBL BNGKG 500</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>20082205</t>
-  </si>
-  <si>
-    <t>SERASOFT SHP HFT 170</t>
+    <t>20067449</t>
+  </si>
+  <si>
+    <t>GLW&amp;LOVELY DRM.GL100</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>20090023</t>
-  </si>
-  <si>
-    <t>WRDH BRGH MUG CLY100</t>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10002941</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH120</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
+    <t>RT,(E-6B)</t>
   </si>
 </sst>
 </file>
@@ -515,7 +521,7 @@
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -575,15 +581,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -592,10 +598,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -615,7 +621,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -635,35 +641,35 @@
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -672,18 +678,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -692,7 +698,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>5</v>
@@ -700,10 +706,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -712,18 +718,18 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -732,10 +738,10 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
   <si>
     <t/>
   </si>
   <si>
-    <t>20055496</t>
-  </si>
-  <si>
-    <t>PRO CHIZ SPRD 160G</t>
+    <t>10005073</t>
+  </si>
+  <si>
+    <t>BLUE BAND PCK 200G</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -31,91 +31,94 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20117107</t>
-  </si>
-  <si>
-    <t>BANGO KECAP MNS 735</t>
+    <t>20032723</t>
+  </si>
+  <si>
+    <t>MILO CEREAL COKLT 30</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20114755</t>
-  </si>
-  <si>
-    <t>SDP MIE SPC.LAKSA 83</t>
+    <t>20093909</t>
+  </si>
+  <si>
+    <t>REBO KUACI MILK 120</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>10023792</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE SOTO 76GR</t>
+    <t>20098348</t>
+  </si>
+  <si>
+    <t>REBO KUACI ORIGNL120</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20047217</t>
-  </si>
-  <si>
-    <t>PEPSODENT WHITE 225G</t>
+    <t>10003569</t>
+  </si>
+  <si>
+    <t>CLOSE UP GRN E.FR160</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20130653</t>
+  </si>
+  <si>
+    <t>SHINZU'I SKURA 380ML</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20021816</t>
+  </si>
+  <si>
+    <t>VSLNE LOT BRIGHT 200</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20138272</t>
-  </si>
-  <si>
-    <t>LRST BB.WIPE SB 2X50</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20041399</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW LMN 400</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20120379</t>
-  </si>
-  <si>
-    <t>EMERON HBL BNGKG 500</t>
+    <t>20018965</t>
+  </si>
+  <si>
+    <t>NIVEA FF DRK.SPT 100</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>20067449</t>
-  </si>
-  <si>
-    <t>GLW&amp;LOVELY DRM.GL100</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20116990</t>
+  </si>
+  <si>
+    <t>POSH DEO ACT COOL 50</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10002941</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH120</t>
+    <t>10000425</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH 60</t>
   </si>
   <si>
     <t>10</t>
@@ -521,7 +524,7 @@
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -581,24 +584,24 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -606,19 +609,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -626,42 +629,42 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -681,15 +684,15 @@
         <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -698,18 +701,18 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -718,18 +721,18 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -738,10 +741,10 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="43">
   <si>
     <t/>
   </si>
   <si>
-    <t>10005073</t>
-  </si>
-  <si>
-    <t>BLUE BAND PCK 200G</t>
+    <t>20045610</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE STO CUP81</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -31,49 +31,55 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20032723</t>
-  </si>
-  <si>
-    <t>MILO CEREAL COKLT 30</t>
+    <t>10008819</t>
+  </si>
+  <si>
+    <t>BANGO KECAP MNS 700G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20093909</t>
-  </si>
-  <si>
-    <t>REBO KUACI MILK 120</t>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>10008882</t>
+  </si>
+  <si>
+    <t>K/API KOPI SPCL 150G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20098348</t>
-  </si>
-  <si>
-    <t>REBO KUACI ORIGNL120</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20047037</t>
+  </si>
+  <si>
+    <t>IDM KACANG BALI 150G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>10003569</t>
-  </si>
-  <si>
-    <t>CLOSE UP GRN E.FR160</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20071105</t>
+  </si>
+  <si>
+    <t>MITU GP PURPLE 2X50S</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20130653</t>
-  </si>
-  <si>
-    <t>SHINZU'I SKURA 380ML</t>
+    <t>20039608</t>
+  </si>
+  <si>
+    <t>MARINA HBL HL&amp;GL 460</t>
   </si>
   <si>
     <t>6</t>
@@ -82,10 +88,10 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20021816</t>
-  </si>
-  <si>
-    <t>VSLNE LOT BRIGHT 200</t>
+    <t>20138899</t>
+  </si>
+  <si>
+    <t>SNSLK SHP G.BLCK 160</t>
   </si>
   <si>
     <t>7</t>
@@ -94,37 +100,46 @@
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20018965</t>
-  </si>
-  <si>
-    <t>NIVEA FF DRK.SPT 100</t>
+    <t>20067449</t>
+  </si>
+  <si>
+    <t>GLW&amp;LOVELY DRM.GL100</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10031825</t>
+  </si>
+  <si>
+    <t>SENSODYNE P/G FM 100</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20027095</t>
+  </si>
+  <si>
+    <t>MY BABY TELON PLS 60</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20116990</t>
-  </si>
-  <si>
-    <t>POSH DEO ACT COOL 50</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10000425</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH 60</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
+    <t>20041621</t>
+  </si>
+  <si>
+    <t>ANTANGIN JRG 5X15ML</t>
+  </si>
+  <si>
+    <t>11</t>
   </si>
 </sst>
 </file>
@@ -517,14 +532,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -584,15 +599,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -601,18 +616,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -621,18 +636,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -641,18 +656,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -661,18 +676,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -681,18 +696,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -701,18 +716,18 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -721,18 +736,18 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -741,10 +756,30 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
   <si>
     <t/>
   </si>
   <si>
-    <t>20045610</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE STO CUP81</t>
+    <t>10038932</t>
+  </si>
+  <si>
+    <t>KPL API SPC MIX 10'S</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -28,43 +28,61 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20130895</t>
+  </si>
+  <si>
+    <t>T/C KPI SS GL.ARN 9S</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20134965</t>
+  </si>
+  <si>
+    <t>TOP/COFF MKACHNO 198</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-5B)</t>
+  </si>
+  <si>
+    <t>20113989</t>
+  </si>
+  <si>
+    <t>ROMA KLP CRM CKL 186</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10008819</t>
-  </si>
-  <si>
-    <t>BANGO KECAP MNS 700G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>10008882</t>
-  </si>
-  <si>
-    <t>K/API KOPI SPCL 150G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20047037</t>
-  </si>
-  <si>
-    <t>IDM KACANG BALI 150G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
+    <t>20105102</t>
+  </si>
+  <si>
+    <t>ROMA KELAPA CRM 174</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20047217</t>
+  </si>
+  <si>
+    <t>PEPSODENT WHITE 225G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
   </si>
   <si>
     <t>20071105</t>
@@ -73,73 +91,85 @@
     <t>MITU GP PURPLE 2X50S</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20039608</t>
-  </si>
-  <si>
-    <t>MARINA HBL HL&amp;GL 460</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20001061</t>
+  </si>
+  <si>
+    <t>MITU G/P PINK 2X50'S</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>10003337</t>
+  </si>
+  <si>
+    <t>EMERON SHP H/F CN170</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10003336</t>
+  </si>
+  <si>
+    <t>EMERON SHP BLK&amp;S 170</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20091271</t>
+  </si>
+  <si>
+    <t>EMRN SHP HJB C&amp;F 170</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20110117</t>
+  </si>
+  <si>
+    <t>G&amp;L FC.FOAM VIT.C100</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20067449</t>
+  </si>
+  <si>
+    <t>GLW&amp;LOVELY DRM.GL100</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20113402</t>
+  </si>
+  <si>
+    <t>KAHF FC.WASH E&amp;B 100</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20138899</t>
-  </si>
-  <si>
-    <t>SNSLK SHP G.BLCK 160</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20067449</t>
-  </si>
-  <si>
-    <t>GLW&amp;LOVELY DRM.GL100</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10031825</t>
-  </si>
-  <si>
-    <t>SENSODYNE P/G FM 100</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20027095</t>
-  </si>
-  <si>
-    <t>MY BABY TELON PLS 60</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20041621</t>
-  </si>
-  <si>
-    <t>ANTANGIN JRG 5X15ML</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>20113403</t>
+  </si>
+  <si>
+    <t>KAHF FC.WASH O&amp;C 100</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
 </sst>
 </file>
@@ -532,14 +562,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -599,135 +629,135 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -736,18 +766,18 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -756,30 +786,110 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="F13" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>13</v>
+      <c r="B14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="60">
   <si>
     <t/>
   </si>
   <si>
-    <t>10038932</t>
-  </si>
-  <si>
-    <t>KPL API SPC MIX 10'S</t>
+    <t>20104000</t>
+  </si>
+  <si>
+    <t>IDM KACANG ALMOND 65</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -28,148 +28,169 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20131802</t>
+  </si>
+  <si>
+    <t>IMPERIAL BLUBERRY108</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20101461</t>
+  </si>
+  <si>
+    <t>ABC KECAP MANIS 825G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20136451</t>
+  </si>
+  <si>
+    <t>NSCAFE AMERICANO 10S</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20093101</t>
+  </si>
+  <si>
+    <t>ZEN BW A.BAC SHIS380</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20130895</t>
-  </si>
-  <si>
-    <t>T/C KPI SS GL.ARN 9S</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20134965</t>
-  </si>
-  <si>
-    <t>TOP/COFF MKACHNO 198</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-5B)</t>
-  </si>
-  <si>
-    <t>20113989</t>
-  </si>
-  <si>
-    <t>ROMA KLP CRM CKL 186</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20105102</t>
-  </si>
-  <si>
-    <t>ROMA KELAPA CRM 174</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20047217</t>
-  </si>
-  <si>
-    <t>PEPSODENT WHITE 225G</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>20081452</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 800</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20071105</t>
-  </si>
-  <si>
-    <t>MITU GP PURPLE 2X50S</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20001061</t>
-  </si>
-  <si>
-    <t>MITU G/P PINK 2X50'S</t>
+    <t>20140968</t>
+  </si>
+  <si>
+    <t>LFBUOY COOL FRS 800</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>10003337</t>
-  </si>
-  <si>
-    <t>EMERON SHP H/F CN170</t>
+    <t>20084152</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW MLD C800</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>10003336</t>
-  </si>
-  <si>
-    <t>EMERON SHP BLK&amp;S 170</t>
+    <t>20087202</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW LMN 800</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>20091271</t>
-  </si>
-  <si>
-    <t>EMRN SHP HJB C&amp;F 170</t>
+    <t>20046908</t>
+  </si>
+  <si>
+    <t>BIORE MEN BRGHT/E100</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>20110117</t>
-  </si>
-  <si>
-    <t>G&amp;L FC.FOAM VIT.C100</t>
+    <t>20046907</t>
+  </si>
+  <si>
+    <t>BIORE MEN COOL/O 100</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>20067449</t>
-  </si>
-  <si>
-    <t>GLW&amp;LOVELY DRM.GL100</t>
+    <t>20133062</t>
+  </si>
+  <si>
+    <t>BIORE MEN B/EXPRT100</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20113402</t>
-  </si>
-  <si>
-    <t>KAHF FC.WASH E&amp;B 100</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20113111</t>
+  </si>
+  <si>
+    <t>BIORE MEN OIL CL 100</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20113403</t>
-  </si>
-  <si>
-    <t>KAHF FC.WASH O&amp;C 100</t>
+    <t>10002941</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH120</t>
   </si>
   <si>
     <t>15</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>10003569</t>
+  </si>
+  <si>
+    <t>CLOSE UP GRN E.FR160</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20135211</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
 </sst>
 </file>
@@ -562,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -629,15 +650,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -646,18 +667,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -666,10 +687,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -689,7 +710,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -729,15 +750,15 @@
         <v>26</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -746,7 +767,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>5</v>
@@ -754,10 +775,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -766,18 +787,18 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -786,18 +807,18 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -806,18 +827,18 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -826,18 +847,18 @@
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -846,30 +867,30 @@
         <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -889,7 +910,47 @@
         <v>52</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="41">
   <si>
     <t/>
   </si>
   <si>
-    <t>20104000</t>
-  </si>
-  <si>
-    <t>IDM KACANG ALMOND 65</t>
+    <t>10022118</t>
+  </si>
+  <si>
+    <t>SUN KARA SANTAN KL65</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -28,13 +28,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20131802</t>
-  </si>
-  <si>
-    <t>IMPERIAL BLUBERRY108</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20138571</t>
+  </si>
+  <si>
+    <t>G/DAY LATTE ORI 10S</t>
   </si>
   <si>
     <t>2</t>
@@ -43,154 +43,97 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20101461</t>
-  </si>
-  <si>
-    <t>ABC KECAP MANIS 825G</t>
+    <t>20138948</t>
+  </si>
+  <si>
+    <t>G/DAY BTRSCOTCH 10S</t>
+  </si>
+  <si>
+    <t>20052583</t>
+  </si>
+  <si>
+    <t>SMYANG GR PDS AYM140</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20136451</t>
-  </si>
-  <si>
-    <t>NSCAFE AMERICANO 10S</t>
+    <t>20113920</t>
+  </si>
+  <si>
+    <t>ME-O TUNA IN JLY 80G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
+    <t>20113921</t>
+  </si>
+  <si>
+    <t>ME-O KITTEN TUNA 80G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20093101</t>
-  </si>
-  <si>
-    <t>ZEN BW A.BAC SHIS380</t>
+    <t>20136708</t>
+  </si>
+  <si>
+    <t>ZINC SHP COOL.BS 170</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20081452</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW RED 800</t>
+    <t>20040608</t>
+  </si>
+  <si>
+    <t>ZINC SHP HFT GNSG170</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
+    <t>20040609</t>
+  </si>
+  <si>
+    <t>ZINC RE-FRSH COOL170</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20067210</t>
+  </si>
+  <si>
+    <t>PONDS PW NSRCNL 100G</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20140968</t>
-  </si>
-  <si>
-    <t>LFBUOY COOL FRS 800</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20084152</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW MLD C800</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20087202</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW LMN 800</t>
+    <t>20067202</t>
+  </si>
+  <si>
+    <t>PONDS PW PR.CHR100G</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>20046908</t>
-  </si>
-  <si>
-    <t>BIORE MEN BRGHT/E100</t>
+    <t>10000425</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH 60</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>20046907</t>
-  </si>
-  <si>
-    <t>BIORE MEN COOL/O 100</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20133062</t>
-  </si>
-  <si>
-    <t>BIORE MEN B/EXPRT100</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20113111</t>
-  </si>
-  <si>
-    <t>BIORE MEN OIL CL 100</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>10002941</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH120</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>10003569</t>
-  </si>
-  <si>
-    <t>CLOSE UP GRN E.FR160</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20135211</t>
-  </si>
-  <si>
-    <t>17</t>
   </si>
 </sst>
 </file>
@@ -583,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -667,27 +610,27 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>9</v>
@@ -695,50 +638,50 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -747,18 +690,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -767,18 +710,18 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -787,18 +730,18 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -807,18 +750,18 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -827,130 +770,30 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="42">
   <si>
     <t/>
   </si>
   <si>
-    <t>10022118</t>
-  </si>
-  <si>
-    <t>SUN KARA SANTAN KL65</t>
+    <t>10022534</t>
+  </si>
+  <si>
+    <t>ABC KCP MNS PCH685G</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -28,112 +28,115 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10008882</t>
+  </si>
+  <si>
+    <t>K/API KOPI SPCL 150G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20068905</t>
+  </si>
+  <si>
+    <t>FF SKM PUTIH 535G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20068906</t>
+  </si>
+  <si>
+    <t>FF SKM COKELAT 535G</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10003569</t>
+  </si>
+  <si>
+    <t>CLOSE UP GRN E.FR160</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20137260</t>
+  </si>
+  <si>
+    <t>B/D FW ACNE CARE 100</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20138571</t>
-  </si>
-  <si>
-    <t>G/DAY LATTE ORI 10S</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138948</t>
-  </si>
-  <si>
-    <t>G/DAY BTRSCOTCH 10S</t>
-  </si>
-  <si>
-    <t>20052583</t>
-  </si>
-  <si>
-    <t>SMYANG GR PDS AYM140</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20113920</t>
-  </si>
-  <si>
-    <t>ME-O TUNA IN JLY 80G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20113921</t>
-  </si>
-  <si>
-    <t>ME-O KITTEN TUNA 80G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20136708</t>
-  </si>
-  <si>
-    <t>ZINC SHP COOL.BS 170</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20040608</t>
-  </si>
-  <si>
-    <t>ZINC SHP HFT GNSG170</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20040609</t>
-  </si>
-  <si>
-    <t>ZINC RE-FRSH COOL170</t>
+    <t>20137413</t>
+  </si>
+  <si>
+    <t>B.DAILY BRIGHT 100</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>20067210</t>
-  </si>
-  <si>
-    <t>PONDS PW NSRCNL 100G</t>
+    <t>20060393</t>
+  </si>
+  <si>
+    <t>NUVO CAIR CLSC 400</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20067202</t>
-  </si>
-  <si>
-    <t>PONDS PW PR.CHR100G</t>
+    <t>10002941</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH120</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>10000425</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH 60</t>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20034577</t>
+  </si>
+  <si>
+    <t>S/M TLK.ANGN+MDU 5'S</t>
   </si>
   <si>
     <t>11</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
   </si>
 </sst>
 </file>
@@ -526,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -610,38 +613,38 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -650,18 +653,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -670,18 +673,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -690,18 +693,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -710,18 +713,18 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -730,18 +733,18 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -750,18 +753,18 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -770,30 +773,10 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="43">
   <si>
     <t/>
   </si>
   <si>
-    <t>10022534</t>
-  </si>
-  <si>
-    <t>ABC KCP MNS PCH685G</t>
+    <t>10005073</t>
+  </si>
+  <si>
+    <t>BLUE BAND PCK 200G</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -28,112 +28,115 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10038932</t>
+  </si>
+  <si>
+    <t>KPL API SPC MIX 10'S</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20107729</t>
+  </si>
+  <si>
+    <t>TOP COFF GL AREN 9'S</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-5B)</t>
+  </si>
+  <si>
+    <t>20095226</t>
+  </si>
+  <si>
+    <t>TOP COFF CAPPCNO 6'S</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20047217</t>
+  </si>
+  <si>
+    <t>PEPSODENT WHITE 225G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10011850</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP MNT DNGN 160</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>PT,(E-5B)</t>
+  </si>
+  <si>
+    <t>20137253</t>
+  </si>
+  <si>
+    <t>BRAVEN EDP COOL 100M</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20054917</t>
+  </si>
+  <si>
+    <t>ELLIP H.VIT K/REP6'S</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>10000425</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH 60</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20053690</t>
+  </si>
+  <si>
+    <t>NIVEA R/ON EXT/WHT50</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>10008882</t>
-  </si>
-  <si>
-    <t>K/API KOPI SPCL 150G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20068905</t>
-  </si>
-  <si>
-    <t>FF SKM PUTIH 535G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20068906</t>
-  </si>
-  <si>
-    <t>FF SKM COKELAT 535G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10003569</t>
-  </si>
-  <si>
-    <t>CLOSE UP GRN E.FR160</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20137260</t>
-  </si>
-  <si>
-    <t>B/D FW ACNE CARE 100</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20137413</t>
-  </si>
-  <si>
-    <t>B.DAILY BRIGHT 100</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20060393</t>
-  </si>
-  <si>
-    <t>NUVO CAIR CLSC 400</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10002941</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH120</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20034577</t>
-  </si>
-  <si>
-    <t>S/M TLK.ANGN+MDU 5'S</t>
+    <t>20083934</t>
+  </si>
+  <si>
+    <t>KOJIESAN SL SOAP 65</t>
   </si>
   <si>
     <t>11</t>
@@ -716,7 +719,7 @@
         <v>31</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -736,15 +739,15 @@
         <v>34</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -753,18 +756,18 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -773,10 +776,10 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
   <si>
     <t/>
   </si>
   <si>
-    <t>10005073</t>
-  </si>
-  <si>
-    <t>BLUE BAND PCK 200G</t>
+    <t>10008819</t>
+  </si>
+  <si>
+    <t>BANGO KECAP MNS 700G</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -28,118 +28,85 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>10008882</t>
+  </si>
+  <si>
+    <t>K/API KOPI SPCL 150G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10038932</t>
-  </si>
-  <si>
-    <t>KPL API SPC MIX 10'S</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20107729</t>
-  </si>
-  <si>
-    <t>TOP COFF GL AREN 9'S</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-5B)</t>
-  </si>
-  <si>
-    <t>20095226</t>
-  </si>
-  <si>
-    <t>TOP COFF CAPPCNO 6'S</t>
+    <t>20002944</t>
+  </si>
+  <si>
+    <t>PPSODENT HERBAL 190G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20047217</t>
-  </si>
-  <si>
-    <t>PEPSODENT WHITE 225G</t>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10002941</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH120</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20021816</t>
+  </si>
+  <si>
+    <t>VSLNE LOT BRIGHT 200</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>10011850</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP MNT DNGN 160</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>PT,(E-5B)</t>
-  </si>
-  <si>
-    <t>20137253</t>
-  </si>
-  <si>
-    <t>BRAVEN EDP COOL 100M</t>
+    <t>20131028</t>
+  </si>
+  <si>
+    <t>ZINC SHP LMN MINT340</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20054917</t>
-  </si>
-  <si>
-    <t>ELLIP H.VIT K/REP6'S</t>
+    <t>20099181</t>
+  </si>
+  <si>
+    <t>ZINC REFRSH COOL 340</t>
   </si>
   <si>
     <t>8</t>
-  </si>
-  <si>
-    <t>10000425</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH 60</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20053690</t>
-  </si>
-  <si>
-    <t>NIVEA R/ON EXT/WHT50</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20083934</t>
-  </si>
-  <si>
-    <t>KOJIESAN SL SOAP 65</t>
-  </si>
-  <si>
-    <t>11</t>
   </si>
 </sst>
 </file>
@@ -532,14 +499,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -639,15 +605,15 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -656,18 +622,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -676,18 +642,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -696,10 +662,10 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -719,67 +685,7 @@
         <v>31</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="41">
   <si>
     <t/>
   </si>
   <si>
-    <t>10008819</t>
-  </si>
-  <si>
-    <t>BANGO KECAP MNS 700G</t>
+    <t>20053052</t>
+  </si>
+  <si>
+    <t>CERES CHO.HZLNUT 180</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -28,85 +28,112 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>10008882</t>
-  </si>
-  <si>
-    <t>K/API KOPI SPCL 150G</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20003902</t>
+  </si>
+  <si>
+    <t>KRAFT CHEDDAR 150G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20094283</t>
+  </si>
+  <si>
+    <t>INDOMILK KM PTH 535G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20120855</t>
+  </si>
+  <si>
+    <t>INDOMILK SWIS CHO535</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20027167</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP400</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20047217</t>
+  </si>
+  <si>
+    <t>PEPSODENT WHITE 225G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20091440</t>
+  </si>
+  <si>
+    <t>CLEAR SHP MENTHOL160</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20009500</t>
+  </si>
+  <si>
+    <t>BIORE B.FOAM RELX400</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20039727</t>
+  </si>
+  <si>
+    <t>SHINZU'I MATSU 380ML</t>
+  </si>
+  <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20002944</t>
-  </si>
-  <si>
-    <t>PPSODENT HERBAL 190G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10002941</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH120</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20021816</t>
-  </si>
-  <si>
-    <t>VSLNE LOT BRIGHT 200</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20131028</t>
-  </si>
-  <si>
-    <t>ZINC SHP LMN MINT340</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20099181</t>
-  </si>
-  <si>
-    <t>ZINC REFRSH COOL 340</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>20039728</t>
+  </si>
+  <si>
+    <t>SHINZU'I KIREI 380ML</t>
+  </si>
+  <si>
+    <t>20130653</t>
+  </si>
+  <si>
+    <t>SHINZU'I SKURA 380ML</t>
+  </si>
+  <si>
+    <t>20134060</t>
+  </si>
+  <si>
+    <t>GLAD2 CLNSR BLBRRY70</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
 </sst>
 </file>
@@ -499,13 +526,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -585,107 +612,187 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>13</v>
+      <c r="B10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="40">
   <si>
     <t/>
   </si>
   <si>
-    <t>20053052</t>
-  </si>
-  <si>
-    <t>CERES CHO.HZLNUT 180</t>
+    <t>10008819</t>
+  </si>
+  <si>
+    <t>BANGO KECAP MNS 700G</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -28,55 +28,94 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20001061</t>
+  </si>
+  <si>
+    <t>MITU G/P PINK 2X50'S</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20071105</t>
+  </si>
+  <si>
+    <t>MITU GP PURPLE 2X50S</t>
+  </si>
+  <si>
+    <t>20036590</t>
+  </si>
+  <si>
+    <t>LUWAK WHT ORGL 9X20</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20003902</t>
-  </si>
-  <si>
-    <t>KRAFT CHEDDAR 150G</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>20073043</t>
+  </si>
+  <si>
+    <t>LUWAK WHT LESS 9'S</t>
+  </si>
+  <si>
+    <t>10011850</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP MNT DNGN 160</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>PT,(E-5B)</t>
+  </si>
+  <si>
+    <t>10025006</t>
+  </si>
+  <si>
+    <t>NESTLE KOKO.COMBO 30</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20094283</t>
-  </si>
-  <si>
-    <t>INDOMILK KM PTH 535G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20120855</t>
-  </si>
-  <si>
-    <t>INDOMILK SWIS CHO535</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20027167</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP400</t>
+    <t>20039728</t>
+  </si>
+  <si>
+    <t>SHINZU'I KIREI 380ML</t>
+  </si>
+  <si>
+    <t>20032723</t>
+  </si>
+  <si>
+    <t>MILO CEREAL COKLT 30</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20047217</t>
-  </si>
-  <si>
-    <t>PEPSODENT WHITE 225G</t>
+    <t>20130653</t>
+  </si>
+  <si>
+    <t>SHINZU'I SKURA 380ML</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20021816</t>
+  </si>
+  <si>
+    <t>VSLNE LOT BRIGHT 200</t>
   </si>
   <si>
     <t>6</t>
@@ -85,55 +124,13 @@
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20091440</t>
-  </si>
-  <si>
-    <t>CLEAR SHP MENTHOL160</t>
+    <t>20113402</t>
+  </si>
+  <si>
+    <t>KAHF FC.WASH E&amp;B 100</t>
   </si>
   <si>
     <t>7</t>
-  </si>
-  <si>
-    <t>20009500</t>
-  </si>
-  <si>
-    <t>BIORE B.FOAM RELX400</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20039727</t>
-  </si>
-  <si>
-    <t>SHINZU'I MATSU 380ML</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20039728</t>
-  </si>
-  <si>
-    <t>SHINZU'I KIREI 380ML</t>
-  </si>
-  <si>
-    <t>20130653</t>
-  </si>
-  <si>
-    <t>SHINZU'I SKURA 380ML</t>
-  </si>
-  <si>
-    <t>20134060</t>
-  </si>
-  <si>
-    <t>GLAD2 CLNSR BLBRRY70</t>
-  </si>
-  <si>
-    <t>9</t>
   </si>
 </sst>
 </file>
@@ -532,7 +529,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -589,19 +586,19 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
@@ -609,39 +606,39 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
@@ -649,58 +646,58 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -709,18 +706,18 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -732,15 +729,15 @@
         <v>29</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -752,47 +749,47 @@
         <v>29</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="42">
   <si>
     <t/>
   </si>
@@ -19,7 +19,7 @@
     <t>10008819</t>
   </si>
   <si>
-    <t>BANGO KECAP MNS 700G</t>
+    <t>BANGO K MANIS 700 G</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -31,106 +31,112 @@
     <t>RT,(E-0.5B)</t>
   </si>
   <si>
-    <t>20001061</t>
-  </si>
-  <si>
-    <t>MITU G/P PINK 2X50'S</t>
+    <t>10038932</t>
+  </si>
+  <si>
+    <t>KAPAPI S MIX 10x23 G</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20071105</t>
-  </si>
-  <si>
-    <t>MITU GP PURPLE 2X50S</t>
-  </si>
-  <si>
-    <t>20036590</t>
-  </si>
-  <si>
-    <t>LUWAK WHT ORGL 9X20</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20073043</t>
-  </si>
-  <si>
-    <t>LUWAK WHT LESS 9'S</t>
-  </si>
-  <si>
-    <t>10011850</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP MNT DNGN 160</t>
+    <t>20032723</t>
+  </si>
+  <si>
+    <t>MILO CRL CKLT 30 G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>PT,(E-5B)</t>
+    <t>RT,(E-1B)</t>
   </si>
   <si>
     <t>10025006</t>
   </si>
   <si>
-    <t>NESTLE KOKO.COMBO 30</t>
+    <t>NSTL KOKO COMBO 30 G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20039728</t>
-  </si>
-  <si>
-    <t>SHINZU'I KIREI 380ML</t>
-  </si>
-  <si>
-    <t>20032723</t>
-  </si>
-  <si>
-    <t>MILO CEREAL COKLT 30</t>
+    <t>20047217</t>
+  </si>
+  <si>
+    <t>PEPSODENT WHI 225 G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20130653</t>
-  </si>
-  <si>
-    <t>SHINZU'I SKURA 380ML</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20021816</t>
-  </si>
-  <si>
-    <t>VSLNE LOT BRIGHT 200</t>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20081452</t>
+  </si>
+  <si>
+    <t>L/BUOY BW RED 800 G</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20113402</t>
-  </si>
-  <si>
-    <t>KAHF FC.WASH E&amp;B 100</t>
+    <t>20087202</t>
+  </si>
+  <si>
+    <t>L/BUOY BW L FR 800 G</t>
+  </si>
+  <si>
+    <t>20091347</t>
+  </si>
+  <si>
+    <t>TRESEMME S KS 170 ML</t>
   </si>
   <si>
     <t>7</t>
+  </si>
+  <si>
+    <t>20112622</t>
+  </si>
+  <si>
+    <t>K.NAT BW CFLO 400 ML</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20120923</t>
+  </si>
+  <si>
+    <t>K.NAT BW SMGN 400 ML</t>
+  </si>
+  <si>
+    <t>20129838</t>
+  </si>
+  <si>
+    <t>K.NAT BW JJ L 400 ML</t>
+  </si>
+  <si>
+    <t>20067449</t>
+  </si>
+  <si>
+    <t>G&amp;L DRM.GL 100 G</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20110117</t>
+  </si>
+  <si>
+    <t>G&amp;L FFOAM V.C 100 G</t>
   </si>
 </sst>
 </file>
@@ -523,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -586,18 +592,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -606,18 +612,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -626,18 +632,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -646,18 +652,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -666,7 +672,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>20</v>
@@ -674,10 +680,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -689,15 +695,15 @@
         <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -706,18 +712,18 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -726,38 +732,38 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -766,30 +772,50 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>32</v>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
   <si>
     <t/>
   </si>
   <si>
-    <t>10008819</t>
-  </si>
-  <si>
-    <t>BANGO K MANIS 700 G</t>
+    <t>20116410</t>
+  </si>
+  <si>
+    <t>CHIKI TWIST CORN 75G</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -28,13 +28,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>10038932</t>
-  </si>
-  <si>
-    <t>KAPAPI S MIX 10x23 G</t>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20046081</t>
+  </si>
+  <si>
+    <t>G/D 3IN1 MCCINO 10'S</t>
   </si>
   <si>
     <t>2</t>
@@ -43,10 +43,10 @@
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20032723</t>
-  </si>
-  <si>
-    <t>MILO CRL CKLT 30 G</t>
+    <t>20055496</t>
+  </si>
+  <si>
+    <t>PRO CHIZ SPRD 160G</t>
   </si>
   <si>
     <t>3</t>
@@ -55,88 +55,70 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10025006</t>
-  </si>
-  <si>
-    <t>NSTL KOKO COMBO 30 G</t>
+    <t>20002944</t>
+  </si>
+  <si>
+    <t>PPSODENT HERBAL 190G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20047217</t>
-  </si>
-  <si>
-    <t>PEPSODENT WHI 225 G</t>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10003569</t>
+  </si>
+  <si>
+    <t>CLOSE UP GRN E.FR160</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
+    <t>20129700</t>
+  </si>
+  <si>
+    <t>LERVIA SBN MILK 400</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20129702</t>
+  </si>
+  <si>
+    <t>LERVIA SBN JOJOBA400</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20021816</t>
+  </si>
+  <si>
+    <t>VSLNE LOT BRIGHT 200</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20081452</t>
-  </si>
-  <si>
-    <t>L/BUOY BW RED 800 G</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20087202</t>
-  </si>
-  <si>
-    <t>L/BUOY BW L FR 800 G</t>
-  </si>
-  <si>
-    <t>20091347</t>
-  </si>
-  <si>
-    <t>TRESEMME S KS 170 ML</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20112622</t>
-  </si>
-  <si>
-    <t>K.NAT BW CFLO 400 ML</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20120923</t>
-  </si>
-  <si>
-    <t>K.NAT BW SMGN 400 ML</t>
-  </si>
-  <si>
-    <t>20129838</t>
-  </si>
-  <si>
-    <t>K.NAT BW JJ L 400 ML</t>
-  </si>
-  <si>
-    <t>20067449</t>
-  </si>
-  <si>
-    <t>G&amp;L DRM.GL 100 G</t>
+    <t>10002941</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH120</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20110117</t>
-  </si>
-  <si>
-    <t>G&amp;L FFOAM V.C 100 G</t>
+    <t>RT,(E-6B)</t>
   </si>
 </sst>
 </file>
@@ -529,13 +511,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -635,27 +617,27 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -675,35 +657,35 @@
         <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -712,18 +694,18 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -732,90 +714,10 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
   <si>
     <t/>
   </si>
   <si>
-    <t>20116410</t>
-  </si>
-  <si>
-    <t>CHIKI TWIST CORN 75G</t>
+    <t>20113341</t>
+  </si>
+  <si>
+    <t>EMINA CHS SLC MOZA5S</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -28,97 +28,94 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20046081</t>
-  </si>
-  <si>
-    <t>G/D 3IN1 MCCINO 10'S</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20121028</t>
+  </si>
+  <si>
+    <t>EMINA SH.CHEESE 150G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20055496</t>
-  </si>
-  <si>
-    <t>PRO CHIZ SPRD 160G</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20032723</t>
+  </si>
+  <si>
+    <t>MILO CEREAL COKLT 30</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20002944</t>
-  </si>
-  <si>
-    <t>PPSODENT HERBAL 190G</t>
+    <t>10025006</t>
+  </si>
+  <si>
+    <t>NESTLE KOKO.COMBO 30</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10003569</t>
-  </si>
-  <si>
-    <t>CLOSE UP GRN E.FR160</t>
+    <t>20118537</t>
+  </si>
+  <si>
+    <t>PSODENT WHT 120+30G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20129700</t>
-  </si>
-  <si>
-    <t>LERVIA SBN MILK 400</t>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20075943</t>
+  </si>
+  <si>
+    <t>MKRZO SHP ALOE&amp;M 170</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20129702</t>
-  </si>
-  <si>
-    <t>LERVIA SBN JOJOBA400</t>
+    <t>20075945</t>
+  </si>
+  <si>
+    <t>MR HR ENG RYL JL 170</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>20021816</t>
-  </si>
-  <si>
-    <t>VSLNE LOT BRIGHT 200</t>
+    <t>20138098</t>
+  </si>
+  <si>
+    <t>SCORA GENTLE CLEAN75</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10002941</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH120</t>
+    <t>20136932</t>
+  </si>
+  <si>
+    <t>CTRA LOT BGKOANG 210</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>RT,(E-6B)</t>
+    <t>20113920</t>
+  </si>
+  <si>
+    <t>ME-O TUNA IN JLY 80G</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -511,13 +508,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -597,127 +595,147 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>35</v>
+      <c r="F11" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="36">
   <si>
     <t/>
   </si>
   <si>
-    <t>20113341</t>
-  </si>
-  <si>
-    <t>EMINA CHS SLC MOZA5S</t>
+    <t>10005073</t>
+  </si>
+  <si>
+    <t>BLUE BAND PCK 200G</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -31,10 +31,10 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20121028</t>
-  </si>
-  <si>
-    <t>EMINA SH.CHEESE 150G</t>
+    <t>10016646</t>
+  </si>
+  <si>
+    <t>INDO/F KECAP MN.R725</t>
   </si>
   <si>
     <t>2</t>
@@ -43,79 +43,82 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20032723</t>
-  </si>
-  <si>
-    <t>MILO CEREAL COKLT 30</t>
+    <t>20097104</t>
+  </si>
+  <si>
+    <t>NEO/CF MCHNO 6+3X20G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>10025006</t>
-  </si>
-  <si>
-    <t>NESTLE KOKO.COMBO 30</t>
+    <t>RT,(E-5B)</t>
+  </si>
+  <si>
+    <t>20047217</t>
+  </si>
+  <si>
+    <t>PEPSODENT WHITE 225G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20118537</t>
-  </si>
-  <si>
-    <t>PSODENT WHT 120+30G</t>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20039728</t>
+  </si>
+  <si>
+    <t>SHINZU'I KIREI 380ML</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20075943</t>
-  </si>
-  <si>
-    <t>MKRZO SHP ALOE&amp;M 170</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20130653</t>
+  </si>
+  <si>
+    <t>SHINZU'I SKURA 380ML</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20075945</t>
-  </si>
-  <si>
-    <t>MR HR ENG RYL JL 170</t>
+    <t>20018965</t>
+  </si>
+  <si>
+    <t>NIVEA FF DRK.SPT 100</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>20138098</t>
-  </si>
-  <si>
-    <t>SCORA GENTLE CLEAN75</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20053183</t>
+  </si>
+  <si>
+    <t>GTSBY STYL POMADE 75</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>20136932</t>
-  </si>
-  <si>
-    <t>CTRA LOT BGKOANG 210</t>
+    <t>10000425</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH 60</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>20113920</t>
-  </si>
-  <si>
-    <t>ME-O TUNA IN JLY 80G</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>RT,(E-6B)</t>
   </si>
 </sst>
 </file>
@@ -508,17 +511,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -537,8 +540,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -554,11 +563,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -574,11 +583,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -594,16 +603,16 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -612,18 +621,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -632,78 +641,78 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -712,30 +721,10 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>9</v>
+      <c r="H10" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
   <si>
     <t/>
   </si>
   <si>
-    <t>10005073</t>
-  </si>
-  <si>
-    <t>BLUE BAND PCK 200G</t>
+    <t>20055496</t>
+  </si>
+  <si>
+    <t>PRO CHIZ SPRD 160G</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -31,94 +31,97 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10016646</t>
-  </si>
-  <si>
-    <t>INDO/F KECAP MN.R725</t>
+    <t>20104077</t>
+  </si>
+  <si>
+    <t>SEDAP KCP SPCL 725G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>20123088</t>
+  </si>
+  <si>
+    <t>SEDAAP KCP MNS 720ML</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>10008882</t>
+  </si>
+  <si>
+    <t>K/API KOPI SPCL 150G</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10012742</t>
+  </si>
+  <si>
+    <t>LISTERINE COOLMIN250</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20097104</t>
-  </si>
-  <si>
-    <t>NEO/CF MCHNO 6+3X20G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-5B)</t>
-  </si>
-  <si>
-    <t>20047217</t>
-  </si>
-  <si>
-    <t>PEPSODENT WHITE 225G</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>20138899</t>
+  </si>
+  <si>
+    <t>SNSLK SHP G.BLCK 160</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20039728</t>
-  </si>
-  <si>
-    <t>SHINZU'I KIREI 380ML</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20130653</t>
-  </si>
-  <si>
-    <t>SHINZU'I SKURA 380ML</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20018965</t>
-  </si>
-  <si>
-    <t>NIVEA FF DRK.SPT 100</t>
+    <t>20060386</t>
+  </si>
+  <si>
+    <t>GIV BW MLB&amp;CLG PC400</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20053183</t>
-  </si>
-  <si>
-    <t>GTSBY STYL POMADE 75</t>
+    <t>20138029</t>
+  </si>
+  <si>
+    <t>GIV BW SAKURA 400ML</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>10000425</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH 60</t>
+    <t>10002941</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH120</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
     <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20062306</t>
+  </si>
+  <si>
+    <t>RXONA MEN DEO ICE 45</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -511,17 +514,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -540,14 +543,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -563,11 +560,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -583,148 +580,168 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="F9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>35</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="39">
   <si>
     <t/>
   </si>
   <si>
-    <t>20055496</t>
-  </si>
-  <si>
-    <t>PRO CHIZ SPRD 160G</t>
+    <t>10016646</t>
+  </si>
+  <si>
+    <t>INDO/F KECAP MN.R725</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -28,85 +28,91 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20036590</t>
+  </si>
+  <si>
+    <t>LUWAK WHT ORGL 9X20</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10004771</t>
+  </si>
+  <si>
+    <t>CERES MILK HAZEL.350</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20002944</t>
+  </si>
+  <si>
+    <t>PPSODENT HERBAL 190G</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20081452</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 800</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20087202</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW LMN 800</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20054917</t>
+  </si>
+  <si>
+    <t>ELLIP H.VIT K/REP6'S</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20138109</t>
+  </si>
+  <si>
+    <t>EVRSNSE XDP GOLD 30</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20104077</t>
-  </si>
-  <si>
-    <t>SEDAP KCP SPCL 725G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20123088</t>
-  </si>
-  <si>
-    <t>SEDAAP KCP MNS 720ML</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10008882</t>
-  </si>
-  <si>
-    <t>K/API KOPI SPCL 150G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10012742</t>
-  </si>
-  <si>
-    <t>LISTERINE COOLMIN250</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20138899</t>
-  </si>
-  <si>
-    <t>SNSLK SHP G.BLCK 160</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20060386</t>
-  </si>
-  <si>
-    <t>GIV BW MLB&amp;CLG PC400</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20138029</t>
-  </si>
-  <si>
-    <t>GIV BW SAKURA 400ML</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>10002941</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH120</t>
+    <t>10000425</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH 60</t>
   </si>
   <si>
     <t>9</t>
@@ -115,10 +121,10 @@
     <t>RT,(E-6B)</t>
   </si>
   <si>
-    <t>20062306</t>
-  </si>
-  <si>
-    <t>RXONA MEN DEO ICE 45</t>
+    <t>20013772</t>
+  </si>
+  <si>
+    <t>JOHNSON COLG SUMR100</t>
   </si>
   <si>
     <t>10</t>
@@ -581,35 +587,35 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -618,18 +624,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -638,30 +644,30 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -681,15 +687,15 @@
         <v>26</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -698,18 +704,18 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -718,18 +724,18 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -738,10 +744,10 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="57">
   <si>
     <t/>
   </si>
   <si>
-    <t>10016646</t>
-  </si>
-  <si>
-    <t>INDO/F KECAP MN.R725</t>
+    <t>20040702</t>
+  </si>
+  <si>
+    <t>PEPSODENT FRSH/CL190</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -28,106 +28,160 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20047217</t>
+  </si>
+  <si>
+    <t>PEPSODENT WHITE 225G</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20040608</t>
+  </si>
+  <si>
+    <t>ZINC SHP HFT GNSG170</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20040609</t>
+  </si>
+  <si>
+    <t>ZINC RE-FRSH COOL170</t>
+  </si>
+  <si>
+    <t>20109265</t>
+  </si>
+  <si>
+    <t>ZINC SHP LMN MINT170</t>
+  </si>
+  <si>
+    <t>20136708</t>
+  </si>
+  <si>
+    <t>ZINC SHP COOL.BS 170</t>
+  </si>
+  <si>
+    <t>20133672</t>
+  </si>
+  <si>
+    <t>HNSUI COL.SUNS.SPF50</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20036590</t>
-  </si>
-  <si>
-    <t>LUWAK WHT ORGL 9X20</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>20056356</t>
+  </si>
+  <si>
+    <t>SHNZUI FW LIGHT 80ML</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>RT,(E-9B)</t>
+  </si>
+  <si>
+    <t>20079010</t>
+  </si>
+  <si>
+    <t>SHNZUI F.WASH TUB 80</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10002941</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH120</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20034577</t>
+  </si>
+  <si>
+    <t>S/M TLK.ANGN+MDU 5'S</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>10004771</t>
-  </si>
-  <si>
-    <t>CERES MILK HAZEL.350</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20002944</t>
-  </si>
-  <si>
-    <t>PPSODENT HERBAL 190G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20081452</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW RED 800</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20087202</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW LMN 800</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20054917</t>
-  </si>
-  <si>
-    <t>ELLIP H.VIT K/REP6'S</t>
+    <t>20095226</t>
+  </si>
+  <si>
+    <t>TOP COFF CAPPCNO 6'S</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20138109</t>
-  </si>
-  <si>
-    <t>EVRSNSE XDP GOLD 30</t>
+    <t>RT,(E-5B)</t>
+  </si>
+  <si>
+    <t>20134965</t>
+  </si>
+  <si>
+    <t>TOP/COFF MKACHNO 198</t>
+  </si>
+  <si>
+    <t>20107729</t>
+  </si>
+  <si>
+    <t>TOP COFF GL AREN 9'S</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10000425</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH 60</t>
+    <t>20003405</t>
+  </si>
+  <si>
+    <t>FORVITA MARGARINE200</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20013772</t>
-  </si>
-  <si>
-    <t>JOHNSON COLG SUMR100</t>
+    <t>20138100</t>
+  </si>
+  <si>
+    <t>FVTA MRGN TUB 200G</t>
+  </si>
+  <si>
+    <t>10000128</t>
+  </si>
+  <si>
+    <t>CERES RICE CLASSIC80</t>
   </si>
   <si>
     <t>10</t>
+  </si>
+  <si>
+    <t>10000129</t>
+  </si>
+  <si>
+    <t>CERES RICE FESTIVE80</t>
   </si>
 </sst>
 </file>
@@ -520,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -584,30 +638,30 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -624,18 +678,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -644,18 +698,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -664,18 +718,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -684,18 +738,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -704,18 +758,18 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -724,30 +778,190 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>5</v>
+      <c r="B13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="36">
   <si>
     <t/>
   </si>
   <si>
-    <t>20104077</t>
-  </si>
-  <si>
-    <t>SEDAP KCP SPCL 725 G</t>
+    <t>20088712</t>
+  </si>
+  <si>
+    <t>SASA SANT.KLP CAIR65</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -28,49 +28,49 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20135312</t>
+  </si>
+  <si>
+    <t>WOW SPAGHETI CARB80</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20123088</t>
-  </si>
-  <si>
-    <t>SEDAAP KCP MS 720 ML</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20036590</t>
-  </si>
-  <si>
-    <t>LUWAK WHT ORG 9x20 G</t>
+    <t>20135313</t>
+  </si>
+  <si>
+    <t>WOW SPAGHETI BOLOG76</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20073043</t>
-  </si>
-  <si>
-    <t>LUWAK WHT LS 9x19 G</t>
+    <t>20137860</t>
+  </si>
+  <si>
+    <t>WOW AGLI OLIO 75G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20041266</t>
-  </si>
-  <si>
-    <t>PSODENT A/COM 190 G</t>
+    <t>20047217</t>
+  </si>
+  <si>
+    <t>PEPSODENT WHITE 225G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>PT,(E-4B)</t>
+    <t>PT,(E-3B)</t>
   </si>
   <si>
     <t>20071105</t>
@@ -85,40 +85,40 @@
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20141206</t>
-  </si>
-  <si>
-    <t>LARISST MN PCK 8X8'S</t>
+    <t>20040609</t>
+  </si>
+  <si>
+    <t>ZINC RE-FRSH COOL170</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20138902</t>
-  </si>
-  <si>
-    <t>SNSLK S S.STH 320 ML</t>
+    <t>20039728</t>
+  </si>
+  <si>
+    <t>SHINZU'I KIREI 380ML</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20009500</t>
-  </si>
-  <si>
-    <t>BIORE BF RELX 400 ML</t>
+    <t>20130653</t>
+  </si>
+  <si>
+    <t>SHINZU'I SKURA 380ML</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
+    <t>20139611</t>
+  </si>
+  <si>
+    <t>FCARE STRONG 15+5ML</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -511,12 +511,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -577,27 +578,27 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -617,7 +618,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -677,47 +678,67 @@
         <v>26</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="F10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>35</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
